--- a/invoices/invoice_2026-07-23.xlsx
+++ b/invoices/invoice_2026-07-23.xlsx
@@ -610,7 +610,7 @@
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>PARTIALLY PAID</t>
         </is>
       </c>
     </row>
@@ -636,7 +636,7 @@
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>PT MITRA BISNIS Indonesia</t>
+          <t>PT KARYA INOVASI Tbk</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>Jl. Gatot Subroto No. 999, Bandung 40123</t>
+          <t>Jl. Thamrin No. 1, Jakarta 10310</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>Budi Santoso | budi@mitraindonesia.com</t>
+          <t>Siti Rahayu | siti@karyainovasi.com</t>
         </is>
       </c>
     </row>
@@ -694,14 +694,14 @@
     <row r="16" ht="28" customHeight="1">
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Project Management</t>
+          <t>API Development</t>
         </is>
       </c>
       <c r="C16" s="12" t="n">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="D16" s="13" t="n">
-        <v>450000</v>
+        <v>900000</v>
       </c>
       <c r="E16" s="14" t="n">
         <v>0.11</v>
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="C17" s="12" t="n">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D17" s="13" t="n">
         <v>250000</v>
@@ -734,14 +734,14 @@
     <row r="18" ht="28" customHeight="1">
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>API Development</t>
+          <t>QA &amp; Testing Services</t>
         </is>
       </c>
       <c r="C18" s="12" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="D18" s="13" t="n">
-        <v>900000</v>
+        <v>350000</v>
       </c>
       <c r="E18" s="14" t="n">
         <v>0.11</v>
@@ -754,14 +754,14 @@
     <row r="19" ht="28" customHeight="1">
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>UI/UX Design Services</t>
+          <t>System Integration &amp; Testing</t>
         </is>
       </c>
       <c r="C19" s="12" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D19" s="13" t="n">
-        <v>750000</v>
+        <v>400000</v>
       </c>
       <c r="E19" s="14" t="n">
         <v>0.11</v>
